--- a/docs/Sprint_Planning_Template.xlsx
+++ b/docs/Sprint_Planning_Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Local_Git_Repository\DCPE_2A_04_GroupB\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0305F97-AE5C-4EB3-97D4-F72F151D8BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{753F4F07-422B-4FCA-B845-334FF0D083F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="64">
   <si>
     <t>Sprint</t>
   </si>
@@ -176,6 +176,66 @@
   </si>
   <si>
     <t>As a Software Developer, I need to define all the different Use Case Diagrams for the Library System</t>
+  </si>
+  <si>
+    <t>Create webpage for library book reservation</t>
+  </si>
+  <si>
+    <t>Basic layout is created and can successfully send packets from front end to back end</t>
+  </si>
+  <si>
+    <t>Create webpage, create functions for library interface</t>
+  </si>
+  <si>
+    <t>Create functions for library interface</t>
+  </si>
+  <si>
+    <t>As a Software Developer, I need to create functions for the library interface so it is easier to integrate</t>
+  </si>
+  <si>
+    <t>Finish creating functions for library, integrate functions for library</t>
+  </si>
+  <si>
+    <t>Intergrate code for library</t>
+  </si>
+  <si>
+    <t>As a Software Developer, I need to create and interface for the physical library and integrate the written code from sprint 3</t>
+  </si>
+  <si>
+    <t>Implement functionality for 75% of the requirements (REQ01-REQ18)</t>
+  </si>
+  <si>
+    <t>Create system test cases, software unit testing, containerise application</t>
+  </si>
+  <si>
+    <t>Functions work individually</t>
+  </si>
+  <si>
+    <t>Create system test cases</t>
+  </si>
+  <si>
+    <t>Create software unit tests</t>
+  </si>
+  <si>
+    <t>Containerise application</t>
+  </si>
+  <si>
+    <t>As a Front End Developer, I need to create an interface for users to place reservations for books</t>
+  </si>
+  <si>
+    <t>As a QA tester, I need to create system test cases for the hardware units of the module</t>
+  </si>
+  <si>
+    <t>As a QA tester, I need to create system test cases for the software units of the module</t>
+  </si>
+  <si>
+    <t>As a Release manager, I need to containerise the application so that it can be run on other systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build and run Docker image in Raspberry Pi </t>
+  </si>
+  <si>
+    <t>Implement test cases for 90% of functions</t>
   </si>
 </sst>
 </file>
@@ -764,7 +824,7 @@
         <v>45437</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="4:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -804,16 +864,18 @@
       <c r="E8" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="4"/>
+      <c r="F8" s="6" t="s">
+        <v>46</v>
+      </c>
       <c r="G8" s="13">
-        <v>44928</v>
+        <v>45101</v>
       </c>
       <c r="H8" s="13">
         <f>G8+11</f>
-        <v>44939</v>
+        <v>45112</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="4:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -823,17 +885,19 @@
       <c r="E9" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="4"/>
+      <c r="F9" s="6" t="s">
+        <v>49</v>
+      </c>
       <c r="G9" s="13">
         <f>G8+14</f>
-        <v>44942</v>
+        <v>45115</v>
       </c>
       <c r="H9" s="13">
         <f>G9+11</f>
-        <v>44953</v>
+        <v>45126</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="4:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -843,17 +907,19 @@
       <c r="E10" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="4"/>
+      <c r="F10" s="6" t="s">
+        <v>53</v>
+      </c>
       <c r="G10" s="13">
         <f t="shared" ref="G10" si="2">G9+14</f>
-        <v>44956</v>
+        <v>45129</v>
       </c>
       <c r="H10" s="13">
         <f t="shared" si="1"/>
-        <v>44967</v>
+        <v>45140</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -887,6 +953,9 @@
   <headerFooter>
     <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;K000000Official (Closed), Sensitive (Normal)&amp;1#</oddHeader>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="E8" twoDigitTextYear="1"/>
+  </ignoredErrors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -1118,91 +1187,171 @@
       <c r="F5" s="6">
         <v>3</v>
       </c>
-      <c r="G5" s="9"/>
+      <c r="G5" s="6">
+        <v>6</v>
+      </c>
       <c r="H5" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B6" s="6">
         <f t="shared" ref="B6:B69" si="0">B5+1</f>
         <v>3</v>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C6" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="6">
+        <v>6</v>
+      </c>
+      <c r="G6" s="6">
+        <v>8</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B7" s="6">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C7" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="6">
+        <v>7</v>
+      </c>
+      <c r="G7" s="6">
+        <v>8</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B8" s="6">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C8" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="6">
+        <v>8</v>
+      </c>
+      <c r="G8" s="6">
+        <v>8</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B9" s="6">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C9" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" s="6">
+        <v>6</v>
+      </c>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B10" s="6">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C10" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="6">
+        <v>6</v>
+      </c>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B11" s="6">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
+      <c r="C11" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" s="6">
+        <v>6</v>
+      </c>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="6">
@@ -1212,8 +1361,8 @@
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
     </row>
@@ -1225,8 +1374,8 @@
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
     </row>
@@ -1238,8 +1387,8 @@
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
     </row>
@@ -1251,8 +1400,8 @@
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
     </row>
@@ -1264,8 +1413,8 @@
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
     </row>
@@ -1277,8 +1426,8 @@
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
     </row>
@@ -1290,8 +1439,8 @@
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
     </row>
@@ -1303,8 +1452,8 @@
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
     </row>
@@ -1316,8 +1465,8 @@
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
     </row>
@@ -1329,8 +1478,8 @@
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
     </row>
@@ -1342,8 +1491,8 @@
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
     </row>
@@ -1355,8 +1504,8 @@
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
     </row>
@@ -1368,8 +1517,8 @@
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
     </row>
@@ -1381,8 +1530,8 @@
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
       <c r="H25" s="6"/>
       <c r="I25" s="6"/>
     </row>
@@ -1394,8 +1543,8 @@
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
     </row>
@@ -1407,8 +1556,8 @@
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
       <c r="H27" s="6"/>
       <c r="I27" s="6"/>
     </row>
@@ -1420,8 +1569,8 @@
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
     </row>
@@ -1433,8 +1582,8 @@
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
       <c r="H29" s="6"/>
       <c r="I29" s="6"/>
     </row>
@@ -1446,8 +1595,8 @@
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
       <c r="H30" s="6"/>
       <c r="I30" s="6"/>
     </row>
@@ -1459,8 +1608,8 @@
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
       <c r="H31" s="6"/>
       <c r="I31" s="6"/>
     </row>
@@ -1472,8 +1621,8 @@
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
       <c r="H32" s="6"/>
       <c r="I32" s="6"/>
     </row>
@@ -1485,8 +1634,8 @@
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
       <c r="H33" s="6"/>
       <c r="I33" s="6"/>
     </row>
@@ -1498,8 +1647,8 @@
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
       <c r="H34" s="6"/>
       <c r="I34" s="6"/>
     </row>
@@ -1511,8 +1660,8 @@
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
       <c r="H35" s="6"/>
       <c r="I35" s="6"/>
     </row>
@@ -1524,8 +1673,8 @@
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
       <c r="H36" s="6"/>
       <c r="I36" s="6"/>
     </row>
@@ -1537,8 +1686,8 @@
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
       <c r="H37" s="6"/>
       <c r="I37" s="6"/>
     </row>
@@ -1550,8 +1699,8 @@
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
       <c r="H38" s="6"/>
       <c r="I38" s="6"/>
     </row>
@@ -1563,8 +1712,8 @@
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
       <c r="H39" s="6"/>
       <c r="I39" s="6"/>
     </row>
@@ -1576,8 +1725,8 @@
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
       <c r="H40" s="6"/>
       <c r="I40" s="6"/>
     </row>
@@ -1589,8 +1738,8 @@
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
       <c r="H41" s="6"/>
       <c r="I41" s="6"/>
     </row>
@@ -1602,8 +1751,8 @@
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
       <c r="H42" s="6"/>
       <c r="I42" s="6"/>
     </row>
@@ -1615,8 +1764,8 @@
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
       <c r="H43" s="6"/>
       <c r="I43" s="6"/>
     </row>
@@ -2333,7 +2482,7 @@
       <c r="F98" s="9"/>
       <c r="G98" s="9"/>
       <c r="H98" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I98" s="6"/>
     </row>
@@ -2514,6 +2663,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E81D8C8DDAE8BD44A422697963F06C45" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b6816e004dbb89c674e51f5647972552">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2b02348f-b4e3-458c-83fc-9e90db0f8029" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e6418ca14ac9ee17b8bbf6df78e0c223" ns2:_="">
     <xsd:import namespace="2b02348f-b4e3-458c-83fc-9e90db0f8029"/>
@@ -2671,35 +2835,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9627D045-E8ED-4A1C-9984-B3567A1079DB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45A76368-52EE-4CED-9A8C-007D3E8E358A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2b02348f-b4e3-458c-83fc-9e90db0f8029"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2721,9 +2860,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45A76368-52EE-4CED-9A8C-007D3E8E358A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9627D045-E8ED-4A1C-9984-B3567A1079DB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2b02348f-b4e3-458c-83fc-9e90db0f8029"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>